--- a/build/model_phase01.xlsx
+++ b/build/model_phase01.xlsx
@@ -44,75 +44,76 @@
     <definedName name="GrowthUtility">'Inputs'!$B$25</definedName>
     <definedName name="GrowthTax">'Inputs'!$B$26</definedName>
     <definedName name="GrowthOther">'Inputs'!$B$27</definedName>
-    <definedName name="LeaseUpIncomeOffset">'Inputs'!$B$30</definedName>
-    <definedName name="UnitsDeliveredPerMo">'Inputs'!$B$31</definedName>
-    <definedName name="UnitsLeasedPerMo">'Inputs'!$B$32</definedName>
-    <definedName name="LeaseUpRampPct">'Inputs'!$B$33</definedName>
-    <definedName name="LeaseUpElevationPct">'Inputs'!$B$34</definedName>
-    <definedName name="StabilizedOccupancy">'Inputs'!$B$35</definedName>
-    <definedName name="LandCost">'Inputs'!$B$38</definedName>
-    <definedName name="GrossAcres">'Inputs'!$B$39</definedName>
-    <definedName name="NetAcres">'Inputs'!$B$40</definedName>
-    <definedName name="FARRatio">'Inputs'!$B$41</definedName>
-    <definedName name="EfficiencyRatio">'Inputs'!$B$42</definedName>
-    <definedName name="ExistingStructureCost">'Inputs'!$B$43</definedName>
-    <definedName name="TaxLevyPct">'Inputs'!$B$46</definedName>
-    <definedName name="TaxAssessmentPct">'Inputs'!$B$47</definedName>
-    <definedName name="TaxValueAdjFactor">'Inputs'!$B$48</definedName>
-    <definedName name="TaxMethodValue">'Inputs'!$B$49</definedName>
-    <definedName name="TaxYear1">'Inputs'!$B$50</definedName>
-    <definedName name="ReassessOnSale">'Inputs'!$B$51</definedName>
-    <definedName name="DispoTaxRatePct">'Inputs'!$B$52</definedName>
-    <definedName name="FundingOrderPari">'Inputs'!$B$55</definedName>
-    <definedName name="TargetLTC">'Inputs'!$B$56</definedName>
-    <definedName name="OpReserveCoverage">'Inputs'!$B$57</definedName>
-    <definedName name="OpReserveMinMonths">'Inputs'!$B$58</definedName>
-    <definedName name="ConLoanTermMonths">'Inputs'!$B$61</definedName>
-    <definedName name="ConRate">'Inputs'!$B$62</definedName>
-    <definedName name="ConActual360">'Inputs'!$B$63</definedName>
-    <definedName name="ConPointsPct">'Inputs'!$B$64</definedName>
-    <definedName name="ConOtherCosts">'Inputs'!$B$65</definedName>
-    <definedName name="ConMinDebtYield">'Inputs'!$B$66</definedName>
-    <definedName name="ConMinDSCR">'Inputs'!$B$67</definedName>
-    <definedName name="LenderReqReserveOverride">'Inputs'!$B$68</definedName>
-    <definedName name="PermMaxLTV">'Inputs'!$B$71</definedName>
-    <definedName name="PermRate">'Inputs'!$B$72</definedName>
-    <definedName name="PermTermMonths">'Inputs'!$B$73</definedName>
-    <definedName name="PermIOMonths">'Inputs'!$B$74</definedName>
-    <definedName name="PermAmortMonths">'Inputs'!$B$75</definedName>
-    <definedName name="PermActual360">'Inputs'!$B$76</definedName>
-    <definedName name="PermPointsPct">'Inputs'!$B$77</definedName>
-    <definedName name="PermMinDebtYield">'Inputs'!$B$78</definedName>
-    <definedName name="PermMinDSCR">'Inputs'!$B$79</definedName>
-    <definedName name="NoCashOut">'Inputs'!$B$80</definedName>
-    <definedName name="RefiMonthOverride">'Inputs'!$B$81</definedName>
-    <definedName name="DevFeePctDirect">'Inputs'!$B$84</definedName>
-    <definedName name="DevFeeThirdPartySplit">'Inputs'!$B$85</definedName>
-    <definedName name="SponsorDispoFeePct">'Inputs'!$B$86</definedName>
-    <definedName name="RecourseFeePct">'Inputs'!$B$87</definedName>
-    <definedName name="BrokerCostPct">'Inputs'!$B$90</definedName>
-    <definedName name="SalesTaxPct">'Inputs'!$B$91</definedName>
-    <definedName name="TaxProrationMonths">'Inputs'!$B$92</definedName>
-    <definedName name="BadDebtPct">'Inputs'!$B$95</definedName>
-    <definedName name="ConcessionsPct">'Inputs'!$B$96</definedName>
-    <definedName name="LossToLeasePct">'Inputs'!$B$97</definedName>
-    <definedName name="ModelUnits">'Inputs'!$B$98</definedName>
-    <definedName name="ParkingPerUnitMo">'Inputs'!$B$99</definedName>
-    <definedName name="RetailIncomeMo">'Inputs'!$B$100</definedName>
-    <definedName name="UtilReimbPerUnitMo">'Inputs'!$B$101</definedName>
-    <definedName name="OtherIncPerUnitMo">'Inputs'!$B$102</definedName>
-    <definedName name="ExpInsurancePerUnit">'Inputs'!$B$105</definedName>
-    <definedName name="ExpUtilitiesPerUnit">'Inputs'!$B$106</definedName>
-    <definedName name="ExpPayrollPerUnit">'Inputs'!$B$107</definedName>
-    <definedName name="ExpRMPerUnit">'Inputs'!$B$108</definedName>
-    <definedName name="ExpTurnoverPerUnit">'Inputs'!$B$109</definedName>
-    <definedName name="ExpContractPerUnit">'Inputs'!$B$110</definedName>
-    <definedName name="ExpAdminPerUnit">'Inputs'!$B$111</definedName>
-    <definedName name="ExpAdvertisingPerUnit">'Inputs'!$B$112</definedName>
-    <definedName name="MgmtFeePct">'Inputs'!$B$113</definedName>
-    <definedName name="CapReservePerUnit">'Inputs'!$B$114</definedName>
-    <definedName name="TaxPrepPerUnit">'Inputs'!$B$115</definedName>
-    <definedName name="AssetMgmtFeePct">'Inputs'!$B$116</definedName>
+    <definedName name="GrowthStartDate">'Inputs'!$B$28</definedName>
+    <definedName name="LeaseUpIncomeOffset">'Inputs'!$B$31</definedName>
+    <definedName name="UnitsDeliveredPerMo">'Inputs'!$B$32</definedName>
+    <definedName name="UnitsLeasedPerMo">'Inputs'!$B$33</definedName>
+    <definedName name="LeaseUpRampPct">'Inputs'!$B$34</definedName>
+    <definedName name="LeaseUpElevationPct">'Inputs'!$B$35</definedName>
+    <definedName name="StabilizedOccupancy">'Inputs'!$B$36</definedName>
+    <definedName name="LandCost">'Inputs'!$B$39</definedName>
+    <definedName name="GrossAcres">'Inputs'!$B$40</definedName>
+    <definedName name="NetAcres">'Inputs'!$B$41</definedName>
+    <definedName name="FARRatio">'Inputs'!$B$42</definedName>
+    <definedName name="EfficiencyRatio">'Inputs'!$B$43</definedName>
+    <definedName name="ExistingStructureCost">'Inputs'!$B$44</definedName>
+    <definedName name="TaxLevyPct">'Inputs'!$B$47</definedName>
+    <definedName name="TaxAssessmentPct">'Inputs'!$B$48</definedName>
+    <definedName name="TaxValueAdjFactor">'Inputs'!$B$49</definedName>
+    <definedName name="TaxMethodValue">'Inputs'!$B$50</definedName>
+    <definedName name="TaxYear1Override">'Inputs'!$B$51</definedName>
+    <definedName name="ReassessOnSale">'Inputs'!$B$52</definedName>
+    <definedName name="DispoTaxRatePct">'Inputs'!$B$53</definedName>
+    <definedName name="FundingOrderPari">'Inputs'!$B$56</definedName>
+    <definedName name="TargetLTC">'Inputs'!$B$57</definedName>
+    <definedName name="OpReserveCoverage">'Inputs'!$B$58</definedName>
+    <definedName name="OpReserveMinMonths">'Inputs'!$B$59</definedName>
+    <definedName name="ConLoanTermMonths">'Inputs'!$B$62</definedName>
+    <definedName name="ConRate">'Inputs'!$B$63</definedName>
+    <definedName name="ConActual360">'Inputs'!$B$64</definedName>
+    <definedName name="ConPointsPct">'Inputs'!$B$65</definedName>
+    <definedName name="ConOtherCosts">'Inputs'!$B$66</definedName>
+    <definedName name="ConMinDebtYield">'Inputs'!$B$67</definedName>
+    <definedName name="ConMinDSCR">'Inputs'!$B$68</definedName>
+    <definedName name="LenderReqReserveOverride">'Inputs'!$B$69</definedName>
+    <definedName name="PermMaxLTV">'Inputs'!$B$72</definedName>
+    <definedName name="PermRate">'Inputs'!$B$73</definedName>
+    <definedName name="PermTermMonths">'Inputs'!$B$74</definedName>
+    <definedName name="PermIOMonths">'Inputs'!$B$75</definedName>
+    <definedName name="PermAmortMonths">'Inputs'!$B$76</definedName>
+    <definedName name="PermActual360">'Inputs'!$B$77</definedName>
+    <definedName name="PermPointsPct">'Inputs'!$B$78</definedName>
+    <definedName name="PermMinDebtYield">'Inputs'!$B$79</definedName>
+    <definedName name="PermMinDSCR">'Inputs'!$B$80</definedName>
+    <definedName name="NoCashOut">'Inputs'!$B$81</definedName>
+    <definedName name="RefiMonthOverride">'Inputs'!$B$82</definedName>
+    <definedName name="DevFeePctDirect">'Inputs'!$B$85</definedName>
+    <definedName name="DevFeeThirdPartySplit">'Inputs'!$B$86</definedName>
+    <definedName name="SponsorDispoFeePct">'Inputs'!$B$87</definedName>
+    <definedName name="RecourseFeePct">'Inputs'!$B$88</definedName>
+    <definedName name="BrokerCostPct">'Inputs'!$B$91</definedName>
+    <definedName name="SalesTaxPct">'Inputs'!$B$92</definedName>
+    <definedName name="TaxProrationMonths">'Inputs'!$B$93</definedName>
+    <definedName name="BadDebtPct">'Inputs'!$B$96</definedName>
+    <definedName name="ConcessionsPct">'Inputs'!$B$97</definedName>
+    <definedName name="LossToLeasePct">'Inputs'!$B$98</definedName>
+    <definedName name="ModelUnits">'Inputs'!$B$99</definedName>
+    <definedName name="ParkingPerUnitMo">'Inputs'!$B$100</definedName>
+    <definedName name="RetailIncomeMo">'Inputs'!$B$101</definedName>
+    <definedName name="UtilReimbPerUnitMo">'Inputs'!$B$102</definedName>
+    <definedName name="OtherIncPerUnitMo">'Inputs'!$B$103</definedName>
+    <definedName name="ExpInsurancePerUnit">'Inputs'!$B$106</definedName>
+    <definedName name="ExpUtilitiesPerUnit">'Inputs'!$B$107</definedName>
+    <definedName name="ExpPayrollPerUnit">'Inputs'!$B$108</definedName>
+    <definedName name="ExpRMPerUnit">'Inputs'!$B$109</definedName>
+    <definedName name="ExpTurnoverPerUnit">'Inputs'!$B$110</definedName>
+    <definedName name="ExpContractPerUnit">'Inputs'!$B$111</definedName>
+    <definedName name="ExpAdminPerUnit">'Inputs'!$B$112</definedName>
+    <definedName name="ExpAdvertisingPerUnit">'Inputs'!$B$113</definedName>
+    <definedName name="MgmtFeePct">'Inputs'!$B$114</definedName>
+    <definedName name="CapReservePerUnit">'Inputs'!$B$115</definedName>
+    <definedName name="TaxPrepPerUnit">'Inputs'!$B$116</definedName>
+    <definedName name="AssetMgmtFeePct">'Inputs'!$B$117</definedName>
     <definedName name="TotalUnits">'UnitMatrix'!$B$14</definedName>
     <definedName name="MarketUnits">'UnitMatrix'!$B$15</definedName>
     <definedName name="LowUnits">'UnitMatrix'!$B$16</definedName>
@@ -122,12 +123,12 @@
     <definedName name="BaseMarketRentMo">'UnitMatrix'!$B$20</definedName>
     <definedName name="BaseLowRentMo">'UnitMatrix'!$B$21</definedName>
     <definedName name="RetailRentMo">'UnitMatrix'!$B$27</definedName>
-    <definedName name="BudgetLand">'Budget'!$I$35</definedName>
-    <definedName name="BudgetSoft">'Budget'!$I$36</definedName>
-    <definedName name="BudgetHard">'Budget'!$I$37</definedName>
-    <definedName name="DirectCosts">'Budget'!$I$38</definedName>
-    <definedName name="DevFee">'Budget'!$I$39</definedName>
-    <definedName name="BudgetTDCref">'Budget'!$I$40</definedName>
+    <definedName name="BudgetLand">'Budget'!$I$34</definedName>
+    <definedName name="BudgetSoft">'Budget'!$I$35</definedName>
+    <definedName name="BudgetHard">'Budget'!$I$36</definedName>
+    <definedName name="DirectCosts">'Budget'!$I$37</definedName>
+    <definedName name="DevFee">'Budget'!$I$38</definedName>
+    <definedName name="BudgetTDCref">'Budget'!$I$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -135,14 +136,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="mmm-yyyy"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot; mo&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="$#,##0;($#,##0)"/>
-    <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0;(#,##0)"/>
-    <numFmt numFmtId="170" formatCode="$#,##0.00;($#,##0.00)"/>
+  <numFmts count="8">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="mmm-yyyy"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot; mo&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="$#,##0;($#,##0)"/>
+    <numFmt numFmtId="169" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="170" formatCode="#,##0;(#,##0)"/>
+    <numFmt numFmtId="171" formatCode="$#,##0.00;($#,##0.00)"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -274,10 +276,10 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -286,16 +288,16 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -307,13 +309,13 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -326,7 +328,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -335,13 +337,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="171" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="170" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -925,10 +927,8 @@
           <t>Inception Date</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+      <c r="B12" s="7" t="n">
+        <v>46023</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -1140,679 +1140,679 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Growth Start Date</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Date all growth trending begins (override)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Unit Delivery &amp; Lease-Up</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Lease Up Income Offset</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>1=offset lease-up income vs equity, 0=no</t>
-        </is>
-      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Units Delivered Per Mo</t>
+          <t>Lease Up Income Offset</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Units delivered per month</t>
+          <t>1=offset lease-up income vs equity, 0=no</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Units Leased Per Mo</t>
+          <t>Units Delivered Per Mo</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Units absorbed (leased) per month</t>
+          <t>Units delivered per month</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Lease Up Ramp Pct</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="n">
-        <v>0.6</v>
+          <t>Units Leased Per Mo</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>18</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Variable-opex ramp: % of stabilized during lease-up</t>
+          <t>Units absorbed (leased) per month</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Lease Up Elevation Pct</t>
+          <t>Lease Up Ramp Pct</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Elevated-opex uplift over stabilized during lease-up</t>
+          <t>Variable-opex ramp: % of stabilized during lease-up</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>Lease Up Elevation Pct</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Elevated-opex uplift over stabilized during lease-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>Stabilized Occupancy</t>
         </is>
       </c>
-      <c r="B35" s="11" t="n">
+      <c r="B36" s="11" t="n">
         <v>0.93</v>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Physical occupancy at stabilization</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Site Details</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Land Cost</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Total land cost</t>
-        </is>
-      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Gross Acres</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="n">
-        <v>9.5</v>
+          <t>Land Cost</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n">
+        <v>14000000</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Gross site acres</t>
+          <t>Total land cost</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Net Acres</t>
+          <t>Gross Acres</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Net developable acres</t>
+          <t>Gross site acres</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>FARRatio</t>
+          <t>Net Acres</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>1.75</v>
+        <v>8</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Floor-area ratio</t>
+          <t>Net developable acres</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Efficiency Ratio</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>0.85</v>
+          <t>FARRatio</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
+        <v>1.75</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Net rentable / gross buildable</t>
+          <t>Floor-area ratio</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>Efficiency Ratio</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Net rentable / gross buildable</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
           <t>Existing Structure Cost</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Demo / existing structure</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Property Taxes</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Tax Levy Pct</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Levy / mill rate (% of assessed)</t>
-        </is>
-      </c>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Tax Assessment Pct</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="n">
-        <v>1</v>
+          <t>Tax Levy Pct</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>0.0185</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Assessment ratio (% of value)</t>
+          <t>Levy / mill rate (% of assessed)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Tax Value Adj Factor</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="n">
+          <t>Tax Assessment Pct</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Value-adjustment factor</t>
+          <t>Assessment ratio (% of value)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Tax Method Value</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="n">
-        <v>1</v>
+          <t>Tax Value Adj Factor</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Post-stab method: 1=value approach, 0=income approach</t>
+          <t>Value-adjustment / abatement factor (1.0 = full unabated tax)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Tax Year1</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="n">
-        <v>650000</v>
+          <t>Tax Method Value</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Year-1 stabilized tax (value approach)</t>
+          <t>Post-stab method: 1=value approach, 0=income approach</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Reassess On Sale</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="n">
-        <v>1</v>
+          <t>Tax Year1 Override</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>1=reassess buyer taxes on sale value, 0=in-place</t>
+          <t>Year-1 stabilized tax: 0=dynamic (stab value x rate), &gt;0=manual</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>Reassess On Sale</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>1=reassess buyer taxes on sale value, 0=in-place</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
           <t>Dispo Tax Rate Pct</t>
         </is>
       </c>
-      <c r="B52" s="9" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Disposition-period effective tax rate on value</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="B53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Buyer tax rate at sale: 0=use operating effective rate (consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Capitalization &amp; Funding</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Funding Order Pari</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>1=pari-passu, 0=equity-first</t>
-        </is>
-      </c>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Target LTC</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="n">
-        <v>0.65</v>
+          <t>Funding Order Pari</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Target construction loan-to-cost</t>
+          <t>1=pari-passu, 0=equity-first</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Op Reserve Coverage</t>
-        </is>
-      </c>
-      <c r="B57" s="14" t="n">
-        <v>1.1</v>
+          <t>Target LTC</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>0.65</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Operating reserve coverage multiple on peak shortfall</t>
+          <t>Target construction loan-to-cost</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
+          <t>Op Reserve Coverage</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Operating reserve coverage multiple on peak shortfall</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
           <t>Op Reserve Min Months</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n">
+      <c r="B59" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Minimum months of stabilized opex floor for reserve</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Construction Loan</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="4" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Con Loan Term Months</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Construction loan term</t>
-        </is>
-      </c>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Con Rate</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="n">
-        <v>0.08500000000000001</v>
+          <t>Con Loan Term Months</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>36</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Construction interest rate (annual)</t>
+          <t>Construction loan term</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Con Actual360</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="n">
-        <v>1</v>
+          <t>Con Rate</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>0.08500000000000001</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>1=Actual/360, 0=30/360</t>
+          <t>Construction interest rate (annual)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Con Points Pct</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="n">
-        <v>0.01</v>
+          <t>Con Actual360</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Origination points</t>
+          <t>1=Actual/360, 0=30/360</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Con Other Costs</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="n">
-        <v>250000</v>
+          <t>Con Points Pct</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>0.01</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Other construction loan costs</t>
+          <t>Origination points</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Con Min Debt Yield</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="n">
-        <v>0.07000000000000001</v>
+          <t>Con Other Costs</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="n">
+        <v>250000</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Min stabilized debt yield (sizing)</t>
+          <t>Other construction loan costs</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Con Min DSCR</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="n">
-        <v>1.2</v>
+          <t>Con Min Debt Yield</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Min DSCR at target (sizing)</t>
+          <t>Min stabilized debt yield (sizing)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>Con Min DSCR</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Min DSCR at target (sizing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
           <t>Lender Req Reserve Override</t>
         </is>
       </c>
-      <c r="B68" s="12" t="n">
+      <c r="B69" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>If &gt;0, overrides computed interest reserve</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Permanent Loan (Refinance)</t>
         </is>
       </c>
-      <c r="B70" s="4" t="n"/>
-      <c r="C70" s="4" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>Perm Max LTV</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Max permanent loan-to-value</t>
-        </is>
-      </c>
+      <c r="B71" s="4" t="n"/>
+      <c r="C71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Perm Rate</t>
+          <t>Perm Max LTV</t>
         </is>
       </c>
       <c r="B72" s="9" t="n">
-        <v>0.0625</v>
+        <v>0.65</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Permanent interest rate (annual)</t>
+          <t>Max permanent loan-to-value</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Perm Term Months</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="n">
-        <v>360</v>
+          <t>Perm Rate</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n">
+        <v>0.0625</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Permanent loan term</t>
+          <t>Permanent interest rate (annual)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Perm IOMonths</t>
+          <t>Perm Term Months</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Permanent interest-only period</t>
+          <t>Permanent loan term</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Perm Amort Months</t>
+          <t>Perm IOMonths</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>360</v>
+        <v>24</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Permanent amortization period</t>
+          <t>Permanent interest-only period</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Perm Actual360</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="n">
-        <v>0</v>
+          <t>Perm Amort Months</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>360</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>1=Actual/360, 0=30/360</t>
+          <t>Permanent amortization period</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Perm Points Pct</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="n">
-        <v>0.0075</v>
+          <t>Perm Actual360</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Permanent loan points</t>
+          <t>1=Actual/360, 0=30/360</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Perm Min Debt Yield</t>
+          <t>Perm Points Pct</t>
         </is>
       </c>
       <c r="B78" s="9" t="n">
-        <v>0.08</v>
+        <v>0.0075</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Min debt yield at refi (sizing)</t>
+          <t>Permanent loan points</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Perm Min DSCR</t>
-        </is>
-      </c>
-      <c r="B79" s="14" t="n">
-        <v>1.15</v>
+          <t>Perm Min Debt Yield</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>0.08</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Min DSCR at refi (sizing)</t>
+          <t>Min debt yield at refi (sizing)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>No Cash Out</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="n">
-        <v>0</v>
+          <t>Perm Min DSCR</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="n">
+        <v>1.15</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>1=size perm so net cash at refi = 0</t>
+          <t>Min DSCR at refi (sizing)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Refi Month Override</t>
+          <t>No Cash Out</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
@@ -1820,176 +1820,176 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
+          <t>1=size perm so net cash at refi = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Refi Month Override</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
           <t>If &gt;0, override refi month (else = con maturity)</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Sponsor Fees</t>
         </is>
       </c>
-      <c r="B83" s="4" t="n"/>
-      <c r="C83" s="4" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>Dev Fee Pct Direct</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Development fee % of direct costs</t>
-        </is>
-      </c>
+      <c r="B84" s="4" t="n"/>
+      <c r="C84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Dev Fee Third Party Split</t>
+          <t>Dev Fee Pct Direct</t>
         </is>
       </c>
       <c r="B85" s="9" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Portion of dev fee paid to 3rd party</t>
+          <t>Development fee % of direct costs</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Sponsor Dispo Fee Pct</t>
+          <t>Dev Fee Third Party Split</t>
         </is>
       </c>
       <c r="B86" s="9" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Sponsor disposition fee % of sale</t>
+          <t>Portion of dev fee paid to 3rd party</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
+          <t>Sponsor Dispo Fee Pct</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Sponsor disposition fee % of sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
           <t>Recourse Fee Pct</t>
         </is>
       </c>
-      <c r="B87" s="9" t="n">
+      <c r="B88" s="9" t="n">
         <v>0.0025</v>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Loan recourse / indemnity fee % of loan</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Disposition &amp; Sale</t>
         </is>
       </c>
-      <c r="B89" s="4" t="n"/>
-      <c r="C89" s="4" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>Broker Cost Pct</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Broker / sale cost % of gross sale</t>
-        </is>
-      </c>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Sales Tax Pct</t>
+          <t>Broker Cost Pct</t>
         </is>
       </c>
       <c r="B91" s="9" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Transfer / sales tax % of gross sale</t>
+          <t>Broker / sale cost % of gross sale</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
+          <t>Sales Tax Pct</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Transfer / sales tax % of gross sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
           <t>Tax Proration Months</t>
         </is>
       </c>
-      <c r="B92" s="8" t="n">
+      <c r="B93" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>Property-tax proration at sale (months)</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>Stabilized Revenue (other income)</t>
         </is>
       </c>
-      <c r="B94" s="4" t="n"/>
-      <c r="C94" s="4" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Bad Debt Pct</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Bad debt % of GPR</t>
-        </is>
-      </c>
+      <c r="B95" s="4" t="n"/>
+      <c r="C95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Concessions Pct</t>
+          <t>Bad Debt Pct</t>
         </is>
       </c>
       <c r="B96" s="9" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Concessions % of GPR</t>
+          <t>Bad debt % of GPR</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Loss To Lease Pct</t>
+          <t>Concessions Pct</t>
         </is>
       </c>
       <c r="B97" s="9" t="n">
@@ -1997,269 +1997,284 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Gain/loss-to-lease % of GPR</t>
+          <t>Concessions % of GPR</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Model Units</t>
-        </is>
-      </c>
-      <c r="B98" s="10" t="n">
-        <v>1</v>
+          <t>Loss To Lease Pct</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="n">
+        <v>0.01</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Down / model units (non-revenue)</t>
+          <t>Gain/loss-to-lease % of GPR</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Parking Per Unit Mo</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="n">
-        <v>35</v>
+          <t>Model Units</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Parking &amp; storage income $/unit/mo</t>
+          <t>Down / model units (non-revenue)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Retail Income Mo</t>
+          <t>Parking Per Unit Mo</t>
         </is>
       </c>
       <c r="B100" s="12" t="n">
-        <v>18000</v>
+        <v>35</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Retail income $/mo (stabilized)</t>
+          <t>Parking &amp; storage income $/unit/mo</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Util Reimb Per Unit Mo</t>
+          <t>Retail Income Mo</t>
         </is>
       </c>
       <c r="B101" s="12" t="n">
-        <v>45</v>
+        <v>18000</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Utility reimbursement $/unit/mo</t>
+          <t>Retail income $/mo (stabilized)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
+          <t>Util Reimb Per Unit Mo</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Utility reimbursement $/unit/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
           <t>Other Inc Per Unit Mo</t>
         </is>
       </c>
-      <c r="B102" s="12" t="n">
+      <c r="B103" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Other income $/unit/mo</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Stabilized Operating Expenses (annual)</t>
         </is>
       </c>
-      <c r="B104" s="4" t="n"/>
-      <c r="C104" s="4" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Exp Insurance Per Unit</t>
-        </is>
-      </c>
-      <c r="B105" s="12" t="n">
-        <v>425</v>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Insurance $/unit/yr</t>
-        </is>
-      </c>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Exp Utilities Per Unit</t>
+          <t>Exp Insurance Per Unit</t>
         </is>
       </c>
       <c r="B106" s="12" t="n">
-        <v>900</v>
+        <v>425</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Utilities $/unit/yr (variable)</t>
+          <t>Insurance $/unit/yr</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Exp Payroll Per Unit</t>
+          <t>Exp Utilities Per Unit</t>
         </is>
       </c>
       <c r="B107" s="12" t="n">
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Payroll $/unit/yr (elevated in lease-up)</t>
+          <t>Utilities $/unit/yr (variable)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Exp RMPer Unit</t>
+          <t>Exp Payroll Per Unit</t>
         </is>
       </c>
       <c r="B108" s="12" t="n">
-        <v>650</v>
+        <v>1300</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Repairs &amp; maintenance $/unit/yr (variable)</t>
+          <t>Payroll $/unit/yr (elevated in lease-up)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Exp Turnover Per Unit</t>
+          <t>Exp RMPer Unit</t>
         </is>
       </c>
       <c r="B109" s="12" t="n">
-        <v>250</v>
+        <v>650</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Turnover $/unit/yr (variable)</t>
+          <t>Repairs &amp; maintenance $/unit/yr (variable)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Exp Contract Per Unit</t>
+          <t>Exp Turnover Per Unit</t>
         </is>
       </c>
       <c r="B110" s="12" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Contract services $/unit/yr (variable)</t>
+          <t>Turnover $/unit/yr (variable)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Exp Admin Per Unit</t>
+          <t>Exp Contract Per Unit</t>
         </is>
       </c>
       <c r="B111" s="12" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; legal $/unit/yr</t>
+          <t>Contract services $/unit/yr (variable)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Exp Advertising Per Unit</t>
+          <t>Exp Admin Per Unit</t>
         </is>
       </c>
       <c r="B112" s="12" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Advertising $/unit/yr (elevated in lease-up)</t>
+          <t>Admin &amp; legal $/unit/yr</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Mgmt Fee Pct</t>
-        </is>
-      </c>
-      <c r="B113" s="9" t="n">
-        <v>0.03</v>
+          <t>Exp Advertising Per Unit</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="n">
+        <v>200</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Management fee % of EGI</t>
+          <t>Advertising $/unit/yr (elevated in lease-up)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Cap Reserve Per Unit</t>
-        </is>
-      </c>
-      <c r="B114" s="12" t="n">
-        <v>250</v>
+          <t>Mgmt Fee Pct</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="n">
+        <v>0.03</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Capital reserves $/unit/yr (below NOI)</t>
+          <t>Management fee % of EGI</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Tax Prep Per Unit</t>
+          <t>Cap Reserve Per Unit</t>
         </is>
       </c>
       <c r="B115" s="12" t="n">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Tax prep $/unit/yr (below NOI)</t>
+          <t>Capital reserves $/unit/yr (below NOI)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
+          <t>Tax Prep Per Unit</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Tax prep $/unit/yr (below NOI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
           <t>Asset Mgmt Fee Pct</t>
         </is>
       </c>
-      <c r="B116" s="9" t="n">
+      <c r="B117" s="9" t="n">
         <v>0.01</v>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>Asset mgmt fee % of EGI (below NOI)</t>
         </is>
@@ -2846,7 +2861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3338,7 +3353,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Property Taxes (Dev)</t>
+          <t>Insurance (Dev)</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -3357,7 +3372,7 @@
         </is>
       </c>
       <c r="E13" s="29" t="n">
-        <v>700000</v>
+        <v>500000</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -3388,26 +3403,26 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Insurance (Dev)</t>
+          <t>GC Contract (Hard)</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>500000</v>
+          <t>sf</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>200</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -3416,7 +3431,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Straight_Line</t>
+          <t>Bell_Curve</t>
         </is>
       </c>
       <c r="H14" s="10" t="n">
@@ -3438,7 +3453,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>GC Contract (Hard)</t>
+          <t>Off-Site Improvements</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -3453,11 +3468,11 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>sf</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>200</v>
+          <t>abs</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>1200000</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
@@ -3466,7 +3481,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Bell_Curve</t>
+          <t>Straight_Line</t>
         </is>
       </c>
       <c r="H15" s="10" t="n">
@@ -3488,7 +3503,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Off-Site Improvements</t>
+          <t>Utilities &amp; Hookups</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -3507,7 +3522,7 @@
         </is>
       </c>
       <c r="E16" s="29" t="n">
-        <v>1200000</v>
+        <v>900000</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -3538,7 +3553,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Utilities &amp; Hookups</t>
+          <t>Builder's Risk</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -3557,7 +3572,7 @@
         </is>
       </c>
       <c r="E17" s="29" t="n">
-        <v>900000</v>
+        <v>350000</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
@@ -3588,7 +3603,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Builder's Risk</t>
+          <t>Hard Cost Contingency</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -3603,11 +3618,11 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>350000</v>
+          <t>sf</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
@@ -3616,7 +3631,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Straight_Line</t>
+          <t>Bell_Curve</t>
         </is>
       </c>
       <c r="H18" s="10" t="n">
@@ -3638,7 +3653,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Hard Cost Contingency</t>
+          <t>GC Fee</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -3657,7 +3672,7 @@
         </is>
       </c>
       <c r="E19" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
@@ -3688,35 +3703,35 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>GC Fee</t>
+          <t>Other Soft Cost 1 - FF&amp;E</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>sf</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E20" s="13" t="n">
-        <v>12</v>
+        <v>800</v>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Bell_Curve</t>
+          <t>Straight_Line</t>
         </is>
       </c>
       <c r="H20" s="10" t="n">
@@ -3738,7 +3753,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Other Soft Cost 1 - FF&amp;E</t>
+          <t>Other Soft Cost 2 - Permits</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -3753,15 +3768,15 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="n">
-        <v>800</v>
+          <t>abs</t>
+        </is>
+      </c>
+      <c r="E21" s="29" t="n">
+        <v>250000</v>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Pre-Construction</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -3788,7 +3803,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Other Soft Cost 2 - Permits</t>
+          <t>Other Soft Cost 3 - Testing</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -3807,11 +3822,11 @@
         </is>
       </c>
       <c r="E22" s="29" t="n">
-        <v>250000</v>
+        <v>120000</v>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -3838,7 +3853,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Other Soft Cost 3 - Testing</t>
+          <t>Other Soft Cost 4</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -3857,7 +3872,7 @@
         </is>
       </c>
       <c r="E23" s="29" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
@@ -3888,7 +3903,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Other Soft Cost 4</t>
+          <t>Other Soft Cost 5</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -3938,7 +3953,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Other Soft Cost 5</t>
+          <t>Other Soft Cost 6</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -3988,17 +4003,17 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Other Soft Cost 6</t>
+          <t>Other Hard Cost 1 - Landscape</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -4007,7 +4022,7 @@
         </is>
       </c>
       <c r="E26" s="29" t="n">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
@@ -4016,7 +4031,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Straight_Line</t>
+          <t>Bell_Curve</t>
         </is>
       </c>
       <c r="H26" s="10" t="n">
@@ -4038,7 +4053,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Other Hard Cost 1 - Landscape</t>
+          <t>Other Hard Cost 2 - Amenity</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -4057,7 +4072,7 @@
         </is>
       </c>
       <c r="E27" s="29" t="n">
-        <v>650000</v>
+        <v>900000</v>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
@@ -4088,7 +4103,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Other Hard Cost 2 - Amenity</t>
+          <t>Other Hard Cost 3 - Signage</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -4107,7 +4122,7 @@
         </is>
       </c>
       <c r="E28" s="29" t="n">
-        <v>900000</v>
+        <v>150000</v>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
@@ -4116,7 +4131,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Bell_Curve</t>
+          <t>Straight_Line</t>
         </is>
       </c>
       <c r="H28" s="10" t="n">
@@ -4138,7 +4153,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Other Hard Cost 3 - Signage</t>
+          <t>Other Hard Cost 4</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -4157,7 +4172,7 @@
         </is>
       </c>
       <c r="E29" s="29" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
@@ -4166,7 +4181,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Straight_Line</t>
+          <t>Bell_Curve</t>
         </is>
       </c>
       <c r="H29" s="10" t="n">
@@ -4188,7 +4203,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Other Hard Cost 4</t>
+          <t>Other Hard Cost 5</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -4238,7 +4253,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Other Hard Cost 5</t>
+          <t>Other Hard Cost 6</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -4285,128 +4300,78 @@
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Other Hard Cost 6</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="E32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Bell_Curve</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="18">
-        <f>IF(D32="abs",E32,IF(D32="unit",E32*TotalUnits,IF(D32="sf",E32*NRSF,E32)))</f>
-        <v/>
-      </c>
-      <c r="J32" s="18">
-        <f>IF(TotalUnits=0,0,I32/TotalUnits)</f>
-        <v/>
-      </c>
-      <c r="K32" s="19">
-        <f>IF(NRSF=0,0,I32/NRSF)</f>
-        <v/>
-      </c>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>Budget Summary</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="23" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Budget Summary</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="n"/>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="I34" s="30">
+        <f>SUMIF(B5:B31,"Land",I5:I31)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="21" t="inlineStr">
         <is>
-          <t>Land</t>
+          <t>Soft Costs</t>
         </is>
       </c>
       <c r="I35" s="30">
-        <f>SUMIF(B5:B32,"Land",I5:I32)</f>
+        <f>SUMIF(B5:B31,"Soft",I5:I31)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
         <is>
-          <t>Soft Costs</t>
+          <t>Hard Costs</t>
         </is>
       </c>
       <c r="I36" s="30">
-        <f>SUMIF(B5:B32,"Soft",I5:I32)</f>
+        <f>SUMIF(B5:B31,"Hard",I5:I31)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="21" t="inlineStr">
         <is>
-          <t>Hard Costs</t>
+          <t>Direct Costs (subtotal)</t>
         </is>
       </c>
       <c r="I37" s="30">
-        <f>SUMIF(B5:B32,"Hard",I5:I32)</f>
+        <f>SUM(I5:I31)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="21" t="inlineStr">
         <is>
-          <t>Direct Costs (subtotal)</t>
+          <t>Sponsor Development Fee</t>
         </is>
       </c>
       <c r="I38" s="30">
-        <f>SUM(I5:I32)</f>
+        <f>DevFeePctDirect*DirectCosts</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
         <is>
-          <t>Sponsor Development Fee</t>
+          <t>Total Development Cost (per Diagnostics)</t>
         </is>
       </c>
       <c r="I39" s="30">
-        <f>DevFeePctDirect*DirectCosts</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>Total Development Cost (per Diagnostics)</t>
-        </is>
-      </c>
-      <c r="I40" s="30">
         <f>TDC_Total</f>
         <v/>
       </c>
